--- a/llms4om_metrics.xlsx
+++ b/llms4om_metrics.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,6 +454,11 @@
           <t>Accuracy</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Threshold</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -465,13 +470,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="E2" t="n">
         <v>0.9</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.8960334374043014</v>
       </c>
     </row>
     <row r="3">
@@ -484,13 +492,16 @@
         <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.9655172413793104</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9655172413793104</v>
+        <v>0.9824561403508771</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.8869373630936206</v>
       </c>
     </row>
     <row r="4">
@@ -503,13 +514,16 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.4782608695652174</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8679245283018868</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9258411435104816</v>
       </c>
     </row>
   </sheetData>
